--- a/data/sports/ncaaf/flat.xlsx
+++ b/data/sports/ncaaf/flat.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ20" headerRowCount="1">
-  <autoFilter ref="A1:DQ20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ26" headerRowCount="1">
+  <autoFilter ref="A1:DQ26"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$20)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$20,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")/(COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"win")+COUNTIFS('Picks'!$BX$2:$BX$20,"&gt;0",'Picks'!$V$2:$V$20,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$20)/SUM('Picks'!$BX$2:$BX$20),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$20)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$20,"&lt;&gt;",'Picks'!$AB$2:$AB$20),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$20,'Picks'!$AM$2:$AM$20,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A14,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A15,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled",'Picks'!$V$2:$V$20,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$20,'Picks'!$H$2:$H$20,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$20,'Picks'!$H$2:$H$20,$A16,'Picks'!$U$2:$U$20,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ20"/>
+  <dimension ref="A1:DQ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7794,6 +7794,1816 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>7dc72ad0b7594d15</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:30Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>401871054</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>136</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.423729</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="P21" s="28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q21" s="28" t="n">
+        <v>0.146351</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>CFB Joint Model (negative_binomial): proj score Kennesaw State Owls 24.4 @ Missouri State Bears 27.6 (Margin +3.2). Possessions: 12.4, HFA: +2.8 pts.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>136</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.423729</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT21" s="24" t="n"/>
+      <c r="CU21" s="24" t="n"/>
+      <c r="CV21" s="24" t="n"/>
+      <c r="CW21" s="24" t="n"/>
+      <c r="CX21" s="24" t="n"/>
+      <c r="CY21" s="24" t="n"/>
+      <c r="CZ21" s="24" t="n"/>
+      <c r="DA21" s="24" t="n"/>
+      <c r="DB21" s="24" t="n"/>
+      <c r="DC21" s="24" t="n"/>
+      <c r="DD21" s="24" t="n"/>
+      <c r="DE21" s="24" t="n"/>
+      <c r="DF21" s="24" t="n"/>
+      <c r="DG21" s="24" t="n"/>
+      <c r="DH21" s="24" t="n"/>
+      <c r="DI21" s="24" t="n"/>
+      <c r="DJ21" s="24" t="n"/>
+      <c r="DK21" s="24" t="n"/>
+      <c r="DL21" s="24" t="n"/>
+      <c r="DM21" s="24" t="n"/>
+      <c r="DN21" s="24" t="n"/>
+      <c r="DO21" s="24" t="n"/>
+      <c r="DP21" s="24" t="n"/>
+      <c r="DQ21" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.42992, "home": 0.57008}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "0202799d865cde7aa684d247c0626c7dbe66bcaa6d424b412b3e58d58b184f52", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>d29297ac144b4b22</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:30Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>401871054</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.619933</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q22" s="28" t="n">
+        <v>0.100702</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Projected home margin +3.2 pts. Spread: Home +3.0 / Away -3.0 -&gt; P(Away cover)=0.362, P(Home cover)=0.620, P(Push)=0.018.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK22" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT22" s="24" t="n"/>
+      <c r="CU22" s="24" t="n"/>
+      <c r="CV22" s="24" t="n"/>
+      <c r="CW22" s="24" t="n"/>
+      <c r="CX22" s="24" t="n"/>
+      <c r="CY22" s="24" t="n"/>
+      <c r="CZ22" s="24" t="n"/>
+      <c r="DA22" s="24" t="n"/>
+      <c r="DB22" s="24" t="n"/>
+      <c r="DC22" s="24" t="n"/>
+      <c r="DD22" s="24" t="n"/>
+      <c r="DE22" s="24" t="n"/>
+      <c r="DF22" s="24" t="n"/>
+      <c r="DG22" s="24" t="n"/>
+      <c r="DH22" s="24" t="n"/>
+      <c r="DI22" s="24" t="n"/>
+      <c r="DJ22" s="24" t="n"/>
+      <c r="DK22" s="24" t="n"/>
+      <c r="DL22" s="24" t="n"/>
+      <c r="DM22" s="24" t="n"/>
+      <c r="DN22" s="24" t="n"/>
+      <c r="DO22" s="24" t="n"/>
+      <c r="DP22" s="24" t="n"/>
+      <c r="DQ22" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.362333, "home": 0.619933, "push": 0.017733}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "b8158d0a0d1f0cf53e982c23796f66fa6048e3be850bff45b7457d36e7bbd08e", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>b8c560dec9f24e3d</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:30Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>401871054</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-115</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.869565</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.534884</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.5412670000000001</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q23" s="28" t="n">
+        <v>0.006383</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Projected total 52.0 pts (Weather adj: +0.0 pts). Total line 52.5 -&gt; P(Over)=0.459, P(Under)=0.541, P(Push)=0.000.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Kennesaw State Owls</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Missouri State Bears</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="BK23" s="26" t="n">
+        <v>-115</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.869565</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.534884</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT23" s="24" t="n"/>
+      <c r="CU23" s="24" t="n"/>
+      <c r="CV23" s="24" t="n"/>
+      <c r="CW23" s="24" t="n"/>
+      <c r="CX23" s="24" t="n"/>
+      <c r="CY23" s="24" t="n"/>
+      <c r="CZ23" s="24" t="n"/>
+      <c r="DA23" s="24" t="n"/>
+      <c r="DB23" s="24" t="n"/>
+      <c r="DC23" s="24" t="n"/>
+      <c r="DD23" s="24" t="n"/>
+      <c r="DE23" s="24" t="n"/>
+      <c r="DF23" s="24" t="n"/>
+      <c r="DG23" s="24" t="n"/>
+      <c r="DH23" s="24" t="n"/>
+      <c r="DI23" s="24" t="n"/>
+      <c r="DJ23" s="24" t="n"/>
+      <c r="DK23" s="24" t="n"/>
+      <c r="DL23" s="24" t="n"/>
+      <c r="DM23" s="24" t="n"/>
+      <c r="DN23" s="24" t="n"/>
+      <c r="DO23" s="24" t="n"/>
+      <c r="DP23" s="24" t="n"/>
+      <c r="DQ23" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"over": 0.458733, "push": 0.0, "under": 0.541267}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "5646ea9610bf0c58a988925f2e66214567bd20988aee4f371e9719f17dd44ca3", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>11aab69f57f54c3f</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>401871068</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>105</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.487805</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.556312</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Q24" s="28" t="n">
+        <v>0.068507</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>CFB Joint Model (negative_binomial): proj score Western Kentucky Hilltoppers 24.3 @ Sam Houston Bearkats 26.9 (Margin +2.6). Possessions: 12.4, HFA: +2.8 pts.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>105</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.487805</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT24" s="24" t="n"/>
+      <c r="CU24" s="24" t="n"/>
+      <c r="CV24" s="24" t="n"/>
+      <c r="CW24" s="24" t="n"/>
+      <c r="CX24" s="24" t="n"/>
+      <c r="CY24" s="24" t="n"/>
+      <c r="CZ24" s="24" t="n"/>
+      <c r="DA24" s="24" t="n"/>
+      <c r="DB24" s="24" t="n"/>
+      <c r="DC24" s="24" t="n"/>
+      <c r="DD24" s="24" t="n"/>
+      <c r="DE24" s="24" t="n"/>
+      <c r="DF24" s="24" t="n"/>
+      <c r="DG24" s="24" t="n"/>
+      <c r="DH24" s="24" t="n"/>
+      <c r="DI24" s="24" t="n"/>
+      <c r="DJ24" s="24" t="n"/>
+      <c r="DK24" s="24" t="n"/>
+      <c r="DL24" s="24" t="n"/>
+      <c r="DM24" s="24" t="n"/>
+      <c r="DN24" s="24" t="n"/>
+      <c r="DO24" s="24" t="n"/>
+      <c r="DP24" s="24" t="n"/>
+      <c r="DQ24" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.443688, "home": 0.556312}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "8d5890fc6c508cd8e5476ddeda248f9f7274f0c7a59545d3ec9a2d4db2af6731", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>0b70d237867745e5</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>401871068</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-105</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.952381</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.512195</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.589133</v>
+      </c>
+      <c r="P25" s="28" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Q25" s="28" t="n">
+        <v>0.07693800000000001</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Projected home margin +2.6 pts. Spread: Home +1.5 / Away -1.5 -&gt; P(Away cover)=0.411, P(Home cover)=0.589, P(Push)=0.000.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK25" s="26" t="n">
+        <v>-105</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.952381</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.512195</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT25" s="24" t="n"/>
+      <c r="CU25" s="24" t="n"/>
+      <c r="CV25" s="24" t="n"/>
+      <c r="CW25" s="24" t="n"/>
+      <c r="CX25" s="24" t="n"/>
+      <c r="CY25" s="24" t="n"/>
+      <c r="CZ25" s="24" t="n"/>
+      <c r="DA25" s="24" t="n"/>
+      <c r="DB25" s="24" t="n"/>
+      <c r="DC25" s="24" t="n"/>
+      <c r="DD25" s="24" t="n"/>
+      <c r="DE25" s="24" t="n"/>
+      <c r="DF25" s="24" t="n"/>
+      <c r="DG25" s="24" t="n"/>
+      <c r="DH25" s="24" t="n"/>
+      <c r="DI25" s="24" t="n"/>
+      <c r="DJ25" s="24" t="n"/>
+      <c r="DK25" s="24" t="n"/>
+      <c r="DL25" s="24" t="n"/>
+      <c r="DM25" s="24" t="n"/>
+      <c r="DN25" s="24" t="n"/>
+      <c r="DO25" s="24" t="n"/>
+      <c r="DP25" s="24" t="n"/>
+      <c r="DQ25" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.410867, "home": 0.589133, "push": 0.0}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "209ae15be0034c466bb93164bac8f58d082222972c4cb399a2315079350ffd1b", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>c2733a99b44d4dfd</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>401871068</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>NCAAF</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>espn_consensus</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="P26" s="28" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Q26" s="28" t="n">
+        <v>0.033969</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Projected total 51.2 pts (Weather adj: +0.0 pts). Total line 52.5 -&gt; P(Over)=0.447, P(Under)=0.553, P(Push)=0.000.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>College football model; multi-market (moneyline, spread, total).</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Western Kentucky Hilltoppers</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Sam Houston Bearkats</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>cfb_key_number_engine</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>cfb-structural-v2</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>cfb-v1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>94ee6b24581446a6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:04.412986+00:00</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="BK26" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT26" s="24" t="n"/>
+      <c r="CU26" s="24" t="n"/>
+      <c r="CV26" s="24" t="n"/>
+      <c r="CW26" s="24" t="n"/>
+      <c r="CX26" s="24" t="n"/>
+      <c r="CY26" s="24" t="n"/>
+      <c r="CZ26" s="24" t="n"/>
+      <c r="DA26" s="24" t="n"/>
+      <c r="DB26" s="24" t="n"/>
+      <c r="DC26" s="24" t="n"/>
+      <c r="DD26" s="24" t="n"/>
+      <c r="DE26" s="24" t="n"/>
+      <c r="DF26" s="24" t="n"/>
+      <c r="DG26" s="24" t="n"/>
+      <c r="DH26" s="24" t="n"/>
+      <c r="DI26" s="24" t="n"/>
+      <c r="DJ26" s="24" t="n"/>
+      <c r="DK26" s="24" t="n"/>
+      <c r="DL26" s="24" t="n"/>
+      <c r="DM26" s="24" t="n"/>
+      <c r="DN26" s="24" t="n"/>
+      <c r="DO26" s="24" t="n"/>
+      <c r="DP26" s="24" t="n"/>
+      <c r="DQ26" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"over": 0.4468, "push": 0.0, "under": 0.5532}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "96c481f1c97a60acc979eb188e5bbc642045ce73d0b7bf4a60378ed7ea18cf2e", "sport": "NCAAF"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/ncaaf/flat.xlsx
+++ b/data/sports/ncaaf/flat.xlsx
@@ -7797,12 +7797,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>7dc72ad0b7594d15</t>
+          <t>5052f56cb22840bb</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.423729</v>
+        <v>0.454545</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.57008</v>
@@ -7862,10 +7862,10 @@
         <v>0.18</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.146351</v>
+        <v>0.115535</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>1</v>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -8020,13 +8020,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.423729</v>
+        <v>0.454545</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -8089,19 +8089,19 @@
       <c r="DP21" s="24" t="n"/>
       <c r="DQ21" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.42992, "home": 0.57008}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "0202799d865cde7aa684d247c0626c7dbe66bcaa6d424b412b3e58d58b184f52", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 2.5, "total_line": 52.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"away": 0.42992, "home": 0.57008}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "49c2aa2450a8c4225742bb9f266f37ea9a2f4ac5645cd0d84d0b573f86c3915a", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>d29297ac144b4b22</t>
+          <t>1798f14a999c48c5</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="J22" s="25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K22" s="24" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Projected home margin +3.2 pts. Spread: Home +3.0 / Away -3.0 -&gt; P(Away cover)=0.362, P(Home cover)=0.620, P(Push)=0.018.</t>
+          <t>Projected home margin +3.2 pts. Spread: Home +2.5 / Away -2.5 -&gt; P(Away cover)=0.380, P(Home cover)=0.620, P(Push)=0.000.</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="BJ22" s="25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BK22" s="26" t="n">
         <v>-108</v>
@@ -8392,19 +8392,19 @@
       <c r="DP22" s="24" t="n"/>
       <c r="DQ22" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.362333, "home": 0.619933, "push": 0.017733}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "b8158d0a0d1f0cf53e982c23796f66fa6048e3be850bff45b7457d36e7bbd08e", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 2.5, "total_line": 52.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"away": 0.380067, "home": 0.619933, "push": 0.0}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "cb37b17c321fd0f5d9426ff86f501ab49da7eb26f03194d8b9739dc2d4a29215", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>b8c560dec9f24e3d</t>
+          <t>59dc5d4db23d4bfc</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -8451,13 +8451,13 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.909091</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.52381</v>
       </c>
       <c r="O23" s="28" t="n">
         <v>0.5412670000000001</v>
@@ -8466,7 +8466,7 @@
         <v>0.18</v>
       </c>
       <c r="Q23" s="28" t="n">
-        <v>0.006383</v>
+        <v>0.017457</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>0</v>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -8626,13 +8626,13 @@
         <v>52.5</v>
       </c>
       <c r="BK23" s="26" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.869565</v>
+        <v>1.909091</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.52381</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -8695,19 +8695,19 @@
       <c r="DP23" s="24" t="n"/>
       <c r="DQ23" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 3.0, "total_line": 52.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"over": 0.458733, "push": 0.0, "under": 0.541267}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "5646ea9610bf0c58a988925f2e66214567bd20988aee4f371e9719f17dd44ca3", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871054", "event_start_utc": "2026-10-14T23:30Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Kennesaw State Owls", "efficiency_gap": 0.657, "elo_away": 1323.5, "elo_home": 1337.5, "elo_home_win_prob": 0.6117, "event_id": "401871054", "game_start_utc": "2026-10-14T23:30Z", "home_field_advantage_points": 2.8, "home_team": "Missouri State Bears", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.4, "projected_home_points": 27.6, "projected_margin_home": 3.2, "projected_possessions": 12.4, "projected_total": 52.0, "stadium_elevation_ft": 500.0, "travel_distance_miles": 0.0, "uncertainty": 0.18, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.4, "mu_home": 27.6, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.84, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 274674114334540486603088602300644985544}, "uinteger": 0}, "spread_home_line": 2.5, "total_line": 52.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"over": 0.458733, "push": 0.0, "under": 0.541267}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "0c29252721b57932e09400faccf9036273c8b07fa8fcaefae9de8f576bcbe189", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>11aab69f57f54c3f</t>
+          <t>7e4ae50f40634929</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>105</v>
+        <v>-108</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2.05</v>
+        <v>1.925926</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.487805</v>
+        <v>0.519231</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.556312</v>
@@ -8767,7 +8767,7 @@
         <v>0.165</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>0.068507</v>
+        <v>0.037081</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>0</v>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8925,13 +8925,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>105</v>
+        <v>-108</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2.05</v>
+        <v>1.925926</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.487805</v>
+        <v>0.519231</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8994,19 +8994,19 @@
       <c r="DP24" s="24" t="n"/>
       <c r="DQ24" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.443688, "home": 0.556312}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "8d5890fc6c508cd8e5476ddeda248f9f7274f0c7a59545d3ec9a2d4db2af6731", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 53.5}, "market_type": "moneyline", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"away": 0.443688, "home": 0.556312}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "8fff438609310223ba120746105ae6e0881304c5162fdaeadaa91bf5119a640b", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>0b70d237867745e5</t>
+          <t>3672008b145c4ecc</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -9053,13 +9053,13 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.952381</v>
+        <v>1.869565</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.512195</v>
+        <v>0.534884</v>
       </c>
       <c r="O25" s="28" t="n">
         <v>0.589133</v>
@@ -9068,7 +9068,7 @@
         <v>0.165</v>
       </c>
       <c r="Q25" s="28" t="n">
-        <v>0.07693800000000001</v>
+        <v>0.054249</v>
       </c>
       <c r="R25" s="26" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -9228,13 +9228,13 @@
         <v>1.5</v>
       </c>
       <c r="BK25" s="26" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.952381</v>
+        <v>1.869565</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.512195</v>
+        <v>0.534884</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -9297,19 +9297,19 @@
       <c r="DP25" s="24" t="n"/>
       <c r="DQ25" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"away": 0.410867, "home": 0.589133, "push": 0.0}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "209ae15be0034c466bb93164bac8f58d082222972c4cb399a2315079350ffd1b", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 53.5}, "market_type": "spread", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"away": 0.410867, "home": 0.589133, "push": 0.0}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "5308bf304fefc9374072a475fecb68c6cdaaec1d93413b008c12a5840a9811ba", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>c2733a99b44d4dfd</t>
+          <t>308311b4ab96407c</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986Z</t>
+          <t>2026-10-14T22:45:18.806508Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="J26" s="25" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="K26" s="24" t="inlineStr">
         <is>
@@ -9356,22 +9356,22 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.892857</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.528302</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.5532</v>
+        <v>0.568733</v>
       </c>
       <c r="P26" s="28" t="n">
         <v>0.165</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.033969</v>
+        <v>0.040431</v>
       </c>
       <c r="R26" s="26" t="n">
         <v>0</v>
@@ -9400,7 +9400,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Projected total 51.2 pts (Weather adj: +0.0 pts). Total line 52.5 -&gt; P(Over)=0.447, P(Under)=0.553, P(Push)=0.000.</t>
+          <t>Projected total 51.2 pts (Weather adj: +0.0 pts). Total line 53.5 -&gt; P(Over)=0.431, P(Under)=0.569, P(Push)=0.000.</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -9418,7 +9418,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:04.412986+00:00</t>
+          <t>2026-10-14T22:45:18.806508+00:00</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -9528,16 +9528,16 @@
         </is>
       </c>
       <c r="BJ26" s="25" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="BK26" s="26" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.892857</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.528302</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -9600,7 +9600,7 @@
       <c r="DP26" s="24" t="n"/>
       <c r="DQ26" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 52.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T05:51:04.412986+00:00", "probabilities": {"over": 0.4468, "push": 0.0, "under": 0.5532}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "96c481f1c97a60acc979eb188e5bbc642045ce73d0b7bf4a60378ed7ea18cf2e", "sport": "NCAAF"}</t>
+          <t>{"artifact_hash": "94ee6b24581446a6", "event_id": "401871068", "event_start_utc": "2026-10-15T00:00Z", "features": {"altitude_fatigue_penalty": 0.0, "away_team": "Western Kentucky Hilltoppers", "efficiency_gap": 1.887, "elo_away": 1283.9, "elo_home": 1269.8, "elo_home_win_prob": 0.5728, "event_id": "401871068", "game_start_utc": "2026-10-15T00:00Z", "home_field_advantage_points": 2.8, "home_team": "Sam Houston Bearkats", "is_dome": false, "is_fbs_vs_fcs": false, "is_neutral_site": false, "projected_away_points": 24.3, "projected_home_points": 26.9, "projected_margin_home": 2.6, "projected_possessions": 12.4, "projected_total": 51.2, "stadium_elevation_ft": 380, "travel_distance_miles": 677.0, "uncertainty": 0.165, "weather_total_adjustment": 0.0}, "historical_source_observation_times_verified": false, "inference_inputs": {"engine_source_sha256": "449ba2f0e86fa9c445730076a0e0bf100fb4914620be53c75c6f3bfe24298f3f", "mu_away": 24.3, "mu_home": 26.9, "parameters": {"distribution_type": "negative_binomial", "margin_sd": 19.375, "n_simulations": 15000, "nb_dispersion": 12.0, "score_correlation": 0.18, "total_sd": 14.8}, "rng_state_before": {"bit_generator": "PCG64", "has_uint32": 0, "state": {"inc": 332724090758049132448979897138935081983, "state": 76712097772508664445518041650443194929}, "uinteger": 0}, "spread_home_line": 1.5, "total_line": 53.5}, "market_type": "total", "model_version": "cfb-structural-v2", "observed_at_utc": "2026-10-14T22:45:18.806508+00:00", "probabilities": {"over": 0.431267, "push": 0.0, "under": 0.568733}, "replay_scope": "Full precision score means, exact engine parameters and original RNG state; upstream feature construction not certified.", "schema": "cfb-joint-replay-v1", "snapshot_hash": "46d0aa370acef17431587f8a87b8587fd75f74d9460c2c42dd877d894d2f04d3", "sport": "NCAAF"}</t>
         </is>
       </c>
     </row>
